--- a/DataTables/DetailText/剧情/028_01曾题名痰迷心窍.xlsx
+++ b/DataTables/DetailText/剧情/028_01曾题名痰迷心窍.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04741DD7-D42B-4F70-83E8-78C20B8CFD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5B0E71-A786-42ED-B2D6-B58192396C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>LineIndex</t>
   </si>
@@ -60,34 +60,16 @@
     <t>Text</t>
   </si>
   <si>
-    <t>subtitle</t>
-  </si>
-  <si>
     <t>left</t>
   </si>
   <si>
-    <t>dim</t>
-  </si>
-  <si>
-    <t>res://Assets/Background/</t>
-  </si>
-  <si>
     <t>dialogue</t>
   </si>
   <si>
-    <t>right</t>
-  </si>
-  <si>
-    <t>hide</t>
-  </si>
-  <si>
     <t>current_scene</t>
   </si>
   <si>
     <t>mid</t>
-  </si>
-  <si>
-    <t>normal</t>
   </si>
   <si>
     <t>PlayOnce</t>
@@ -184,12 +166,63 @@
     <t>Music</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>028_01</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>曾题名痰火扰心</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>clinic</t>
+  </si>
+  <si>
+    <t>zeng_ti_ming</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>痰迷心窍</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/zeng_ti_ming/zeng_ti_ming.png</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>曾题名</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>李东璧</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>曾和</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大夫啊，您快帮忙看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语考中了考中了的…</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>别急，坐下来让我看看。</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +278,19 @@
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="BIZ UDGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="7">
@@ -322,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -393,6 +439,17 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,8 +666,8 @@
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
     <col min="3" max="3" width="8.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.125" customWidth="1"/>
     <col min="5" max="8" width="8.375" bestFit="1" customWidth="1"/>
@@ -618,8 +675,8 @@
     <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.625" customWidth="1"/>
     <col min="15" max="15" width="26.75" customWidth="1"/>
     <col min="16" max="18" width="8.375" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="10.625" customWidth="1"/>
@@ -627,86 +684,104 @@
   <sheetData>
     <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="18" t="s">
+      <c r="L1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="O1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+      <c r="A2" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="S1" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
       <c r="D2" s="23"/>
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
       <c r="H2" s="23"/>
-      <c r="I2" s="22"/>
+      <c r="I2" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
+      <c r="L2" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>38</v>
+      </c>
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
+      <c r="S2" s="24" t="b">
+        <v>1</v>
+      </c>
       <c r="T2" s="24"/>
     </row>
     <row r="3" spans="1:20">
@@ -946,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -986,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -994,20 +1069,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="29" t="s">
+        <v>43</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9">
@@ -1015,20 +1092,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="29" t="s">
+        <v>44</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9">
@@ -1036,18 +1113,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>41</v>
+      </c>
       <c r="D4" s="7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="7"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="29" t="s">
+        <v>45</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9">
@@ -1055,7 +1134,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2"/>
@@ -1089,6 +1168,94 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/DetailText/剧情/028_01曾题名痰迷心窍.xlsx
+++ b/DataTables/DetailText/剧情/028_01曾题名痰迷心窍.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5B0E71-A786-42ED-B2D6-B58192396C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C039CF7-9712-4D72-8369-FC7FACFD183D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -206,15 +193,15 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>大夫啊，您快帮忙看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语考中了考中了的…</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>…</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>别急，坐下来让我看看。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -453,7 +440,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -664,7 +651,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -682,7 +669,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
@@ -744,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="25" t="s">
         <v>33</v>
       </c>
@@ -1064,7 +1051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1083,7 +1070,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1104,7 +1091,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1125,7 +1112,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I4" s="1"/>
     </row>
